--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.69508877022954</v>
+        <v>3.2004519251623</v>
       </c>
       <c r="D2" t="n">
-        <v>5.505737042543966</v>
+        <v>0.8946822694133946</v>
       </c>
       <c r="E2" t="n">
-        <v>10.03154733621551</v>
+        <v>1.630126442135021</v>
       </c>
       <c r="F2" t="n">
-        <v>9.265264537307994</v>
+        <v>1.505605487312549</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.22002002566218</v>
+        <v>3.610753254170105</v>
       </c>
       <c r="D3" t="n">
-        <v>12.27974725755991</v>
+        <v>1.995458929353485</v>
       </c>
       <c r="E3" t="n">
-        <v>10.03154733621551</v>
+        <v>1.630126442135021</v>
       </c>
       <c r="F3" t="n">
-        <v>9.265264537307994</v>
+        <v>1.505605487312549</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.511811937419951</v>
+        <v>1.383169439830742</v>
       </c>
       <c r="D4" t="n">
-        <v>8.776839805062744</v>
+        <v>1.426236468322696</v>
       </c>
       <c r="E4" t="n">
-        <v>10.03154733621551</v>
+        <v>1.630126442135021</v>
       </c>
       <c r="F4" t="n">
-        <v>9.265264537307994</v>
+        <v>1.505605487312549</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.86936956940976</v>
+        <v>3.391272555029085</v>
       </c>
       <c r="D5" t="n">
-        <v>7.623067741524978</v>
+        <v>1.238748507997809</v>
       </c>
       <c r="E5" t="n">
-        <v>10.03154733621551</v>
+        <v>1.630126442135021</v>
       </c>
       <c r="F5" t="n">
-        <v>9.265264537307994</v>
+        <v>1.505605487312549</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.74274675534632</v>
+        <v>6.458196347743778</v>
       </c>
       <c r="D6" t="n">
-        <v>31.05013866492565</v>
+        <v>5.045647533050419</v>
       </c>
       <c r="E6" t="n">
-        <v>10.03154733621551</v>
+        <v>1.630126442135021</v>
       </c>
       <c r="F6" t="n">
-        <v>9.265264537307994</v>
+        <v>1.505605487312549</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
